--- a/apps/archetest/docs/question-review/question-review-rare.xlsx
+++ b/apps/archetest/docs/question-review/question-review-rare.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Инструкция" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Вопросы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Вопросы'!$A$1:$K$31</definedName>
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,9 +95,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -470,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -479,155 +471,84 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Ревью вопросов Архетеста — добор редких шкал ядра: 30 новых вопросов (SAD 9, ASD 8, MAS 7, ALX 6)</t>
+          <t>Авторские вопросы Archetest — редакция v2, 2026-10-16</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Проведено внутреннее содержательное ревью Codex; это не заключение комиссии психологов.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>⚠️ Этих вопросов ЕЩЁ НЕТ в тесте. Срока нет.</t>
+          <t>Отчёт: prepared-batches-review-2026-10-16.md и JSON с исходниками, ключами и замечаниями.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Пакеты включены в рабочий банк для пилота. Интервью и эмпирическая валидация не проведены.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Зачем:</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Период: последние шесть месяцев; варианты: никогда / редко / часто / почти каждый раз.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>У четырёх шкал в банке меньше 30 вопросов — это порог высокой достоверности результата.</t>
+          <t>Нет подходящих ситуаций или трудно ответить — пропуск, а не нулевой балл.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Садизм — 21 вопрос, систематизация — 22, мазохизм — 23, алекситимия — 24. Пользователь набирает</t>
+          <t>СДВГ: обычные условия с привычной поддержкой; 9 областей INA и 9 HYI; это не ASRS.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>по ним единицы ответов, и высокая достоверность недостижима в принципе. Добор закрывает дефицит.</t>
+          <t>Привязанность: одни выбранные безопасные близкие отношения; без вывода о стиле.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>HON: честность–скромность, четыре фасета; не Agreeableness и не тест нравственности.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Отличие от пакетов СДВГ и привязанности:</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>HON имеет обратный ключ 3/2/1/0; остальные новые пункты — прямой 0/1/2/3.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Это вопросы ТЕХ ЖЕ шкал ядра, стиль и логика — как в пакете 5.1 (основная шкала + правдоподобные</t>
+          <t>Стратегии помощи, вежливость, экономия и разумные границы сами по себе не дают баллов.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>баллы других шкал в остальных вариантах). Критерии — те же, что для 5.1 (INSTRUCTIONS.md).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Их вливание меняет расчёт шкал, поэтому пройдёт одной пачкой после ваших вердиктов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Коротко по таблице:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• Один вопрос = одна строка, варианты А–Г с баллами в скобках.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>• «Обр.» = да — основной балл набирается вариантом, который не выглядит «тёмным» или проблемным</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  с первого взгляда («пишу безжалостный разбор — это же честная обратная связь»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>• «Вердикт»: ОК / Править / Удалить. «Комментарий / правка» — прямо в ячейке.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Особое внимание:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>1. Садизм: не пересекается ли вопрос с антисоциальностью или макиавеллизмом сильнее, чем нужно?</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>2. Мазохизм — авторский конструкт с меткой «бета»: узнаётся ли в вариантах самоотверженность</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   через отказ себе, а не просто скромность или зависимость?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3. Социальная желательность: где «здоровый» вариант слишком очевиден — отметьте.</t>
+          <t>Следующий этап: реальные когнитивные интервью и проверка измерительных свойств.</t>
         </is>
       </c>
     </row>
@@ -721,7 +642,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Удовольствие от унижения</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -732,35 +653,43 @@
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Коллега, который вечно всех поучает, при всех перепутал простой факт и покраснел.</t>
+          <t>За последние шесть месяцев как часто чужая неловкость на глазах у других доставляет вам удовольствие именно потому, что человеку неприятно? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>Смакую момент — и не спешу выручать
-[SAD 3, NAR 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>Тихо подскажу верный ответ, чтобы замять
-[HUM 2]</t>
+          <t>Редко
+[SAD 1]</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Поправлю вслух: факты важнее неловкости
-[DIR 2, OBC 1]</t>
+          <t>Часто
+[SAD 2]</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>Отмечу про себя «так ему и надо», но вида не подам
-[SAD 1, PAG 2]</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[SAD 3]</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -768,7 +697,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Продление страдания</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -776,42 +705,46 @@
           <t>SAD</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="inlineStr"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Вы учите новичка, и он в пятый раз ошибается в одном и том же.</t>
+          <t>За последние шесть месяцев как часто вы намеренно затягиваете неприятный для другого человека момент, чтобы подольше наблюдать его растерянность? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>Объясняю ещё раз, другими словами
-[HUM 1, KAN 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>Говорю «ничего страшного», а сам(а) чуть растягиваю паузу, глядя, как он мучается
+          <t>Редко
+[SAD 1]</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[SAD 2]</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [SAD 3]</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Проще сделать самому (самой)
-[NAR 1, OBC 1]</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>Жёстко отчитываю: пусть запомнит
-[ANT 1, SAD 1]</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -819,7 +752,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Испуг ради удовольствия</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -830,35 +763,43 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Друг до ужаса боится пауков. На даче вы находите огромного паука.</t>
+          <t>За последние шесть месяцев как часто вы намеренно пугаете человека тем, чего он боится, именно ради удовольствия от его испуга? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Позову друга «посмотреть кое-что интересное» — его реакция будет бесценна
-[SAD 3, HIS 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>Выношу паука подальше, пока друг не увидел
-[HUM 2]</t>
+          <t>Редко
+[SAD 1]</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Фотографирую: паук правда интересный
-[SZT 1, ASD 1]</t>
+          <t>Часто
+[SAD 2]</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Предупреждаю друга, чтобы обходил это место
-[KAN 1, HUM 1]</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[SAD 3]</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -866,7 +807,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Давление ради удовольствия</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -877,35 +818,43 @@
       <c r="D5" s="4" t="inlineStr"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>На переговорах вы видите, что человек напротив загнан в угол и нервничает.</t>
+          <t>За последние шесть месяцев как часто добившись нужного решения в споре, вы продолжаете давить на человека, потому что вам приятно видеть его беспомощность? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Дожимаю медленно, без спешки: мне нравится этот момент
-[SAD 3, MAC 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Беру своё и даю ему сохранить лицо
-[MAC 1, HUM 1]</t>
+          <t>Редко
+[SAD 1]</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Иду навстречу: давить на слабого неприятно
-[HUM 2]</t>
+          <t>Часто
+[SAD 2]</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Фиксирую условия письменно — эмоции меня не касаются
-[OBC 2]</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[SAD 3]</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -913,7 +862,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Публичное унижение</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -924,35 +873,43 @@
       <c r="D6" s="4" t="inlineStr"/>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Человек в очереди громко скандалит и явно выставляет себя на посмешище.</t>
+          <t>За последние шесть месяцев как часто вы делитесь чужой неловкой историей без согласия человека ради удовольствия от того, что над ним будут смеяться? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Снимаю на телефон — выложу, пусть посмеются все
-[SAD 3, ANT 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Отворачиваюсь: неловко за человека
-[HUM 1, AVD 1]</t>
+          <t>Редко
+[SAD 1]</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Пытаюсь его успокоить
-[HUM 2]</t>
+          <t>Часто
+[SAD 2]</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Раздражаюсь: зачем устраивать шоу
-[PAG 1, OBC 1]</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr"/>
-      <c r="K6" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[SAD 3]</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -960,7 +917,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Удовольствие от беды</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -968,42 +925,46 @@
           <t>SAD</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D7" s="4" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Бывший партнёр, расставшийся с вами некрасиво, пишет, что у него(неё) всё рушится.</t>
+          <t>За последние шесть месяцев как часто вы расспрашиваете о чужих неприятностях именно потому, что чужое страдание доставляет вам удовольствие? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Отвечаю вежливо и сухо, а внутри — тихое удовольствие от каждой подробности
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[SAD 1]</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[SAD 2]</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [SAD 3]</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Сочувствую искренне: прошлое прошло
-[HUM 2, FAI 1]</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Не отвечаю: это больше не моя история
-[SZD 1, AVD 1]</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>Отвечаю колко: сам(а) виноват(а)
-[PAG 2, SAD 1]</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1011,7 +972,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Досада в игре</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1022,35 +983,43 @@
       <c r="D8" s="4" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Настольная игра с друзьями. Один из них очень переживает, когда проигрывает.</t>
+          <t>За последние шесть месяцев как часто в игре вы специально задеваете соперника, чтобы получить удовольствие от его огорчения, даже когда это не помогает победить? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Играю против него особенно жёстко: его досада — лучшая часть вечера
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[SAD 1]</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[SAD 2]</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [SAD 3]</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Иногда подыгрываю, чтобы всем было весело
-[HUM 2]</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Играю как обычно: игра есть игра
-[KAN 1]</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>Предлагаю командный режим — без проигравших
-[HUM 1, FAI 1]</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr"/>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1058,7 +1027,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Ранящая критика</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1066,42 +1035,46 @@
           <t>SAD</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Знакомый просит отзыв на свой рассказ — рассказ откровенно слабый.</t>
+          <t>За последние шесть месяцев как часто давая отзыв, вы намеренно выбираете обидные выражения ради удовольствия от того, что человеку станет больно? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Пишу подробный и безжалостный разбор — это же честная обратная связь
-[SAD 3, DIR 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Отмечаю сильные стороны и пару главных точек роста
-[HUM 2]</t>
+          <t>Редко
+[SAD 1]</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Говорю, что всё отлично: не хочу расстраивать
-[DEP 1, AVD 1]</t>
+          <t>Часто
+[SAD 2]</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Пишу коротко и по делу
-[DIR 2]</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[SAD 3]</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1109,7 +1082,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Садизм</t>
+          <t>Наблюдение за отказом</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1120,35 +1093,43 @@
       <c r="D10" s="4" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Вы видите, как кто-то неловко пытается познакомиться и получает отказ.</t>
+          <t>За последние шесть месяцев как часто наблюдая, как человеку отказывают, вы хотите, чтобы неловкость продолжалась, потому что вам приятно на неё смотреть? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Смотрю с удовольствием: чужой провал — лучшее кино
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[SAD 1]</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[SAD 2]</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [SAD 3]</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Сочувствую: сам(а) бывал(а) в такой ситуации
-[HUM 2]</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Отвожу взгляд, чтобы не смущать
-[HUM 1, AVD 1]</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Мысленно разбираю, что он(а) сделал(а) не так
-[MAC 1]</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr"/>
-      <c r="K10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1156,7 +1137,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Неопределённое время</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1167,35 +1148,43 @@
       <c r="D11" s="4" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Друг просит «заскочить ненадолго».</t>
+          <t>За последние шесть месяцев как часто в обычной договорённости без точного времени вам трудно понять, когда от вас ожидают действия, даже если контекст знаком? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Уточняю: «ненадолго» — это сколько минут?
-[ASD 3, OBC 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Заезжаю, как получится
-[HIS 1]</t>
+          <t>Редко
+[ASD 1]</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Понятно, минут на двадцать — так обычно и бывает
-[FAI 1]</t>
+          <t>Часто
+[ASD 2]</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, но планирую уйти через час
-[OBC 1]</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[ASD 3]</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1203,7 +1192,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Изменение привычного</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1214,35 +1203,43 @@
       <c r="D12" s="4" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>В любимом кафе сменили меню и расставили столы по-новому.</t>
+          <t>За последние шесть месяцев как часто небольшое неожиданное изменение привычной обстановки надолго затрудняет возвращение к обычным делам? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Выбит(а) из колеи: теперь это будто чужое место
-[ASD 3, AVD 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Интересно — попробую новое
-[HIS 1, FAI 1]</t>
+          <t>Редко
+[ASD 1]</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Замечаю, но мне всё равно
-[SZD 1]</t>
+          <t>Часто
+[ASD 2]</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Пишу отзыв: раньше было лучше
-[PAG 1, OBC 1]</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr"/>
-      <c r="K12" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[ASD 3]</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1250,7 +1247,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Смена тем</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1258,42 +1255,46 @@
           <t>ASD</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D13" s="4" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Небольшая компания, общий разговор легко перескакивает с темы на тему.</t>
+          <t>За последние шесть месяцев как часто в непринуждённом разговоре со знакомыми вам трудно следить за сменой тем, даже когда вы не волнуетесь? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Заранее держу в голове пару тем и фраз — без «сценария» теряюсь
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ASD 1]</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ASD 2]</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ASD 3]</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>Подхватываю легко
-[HIS 1]</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Молчу и слушаю
-[SZD 1, AVD 1]</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Жду повода заговорить о своей теме
-[ASD 2, NAR 1]</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1301,7 +1302,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Переход от деталей к целому</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1312,35 +1313,43 @@
       <c r="D14" s="4" t="inlineStr"/>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Вы собираете мебель по инструкции, а в ней явная ошибка в нумерации деталей.</t>
+          <t>За последние шесть месяцев как часто разбираясь с предметом или системой, вы застреваете на одной детали и с трудом возвращаетесь к общей задаче? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Не успокоюсь, пока не найду, где именно ошибка, и не отмечу её в инструкции
-[ASD 3, OBC 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Собираю по картинке — нумерация неважна
-[]</t>
+          <t>Редко
+[ASD 1]</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Злюсь на производителя и пишу жалобу
-[PAG 2]</t>
+          <t>Часто
+[ASD 2]</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Прошу кого-нибудь помочь
-[DEP 2]</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[ASD 3]</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1348,7 +1357,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Подготовка к новому</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1356,42 +1365,46 @@
           <t>ASD</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Вечер пятницы. Друзья зовут в бар, где вы ещё не бывали.</t>
+          <t>За последние шесть месяцев как часто в новом, но безопасном и доступном месте вам трудно освоиться даже после того, как вы узнали необходимую практическую информацию? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, но заранее смотрю фото зала, меню и как добираться — так спокойнее
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ASD 1]</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ASD 2]</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ASD 3]</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>Иду с удовольствием — люблю новые места
-[HIS 2]</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Не пойду: вечер пятницы — моё время
-[SZD 2]</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>Пойду, если там будет кто-то из близких
-[DEP 1, AVD 1]</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1399,7 +1412,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Неявный смысл</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1410,35 +1423,43 @@
       <c r="D16" s="4" t="inlineStr"/>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Вас просят «сделать как обычно, только немного лучше».</t>
+          <t>За последние шесть месяцев как часто в знакомой ситуации вам трудно понять непрямую просьбу, хотя все необходимые слова вы знаете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Теряюсь: «лучше» — это по каким параметрам?
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ASD 1]</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ASD 2]</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ASD 3]</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>Интуитивно понимаю, что имеется в виду, и делаю
-[]</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Делаю по-своему — я лучше знаю
-[NAR 2]</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Боюсь не угадать и переделываю несколько раз
-[DEP 2]</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1446,7 +1467,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Сигналы собеседника</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1457,35 +1478,43 @@
       <c r="D17" s="4" t="inlineStr"/>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Вы долго объясняли собеседнику устройство интересной вам системы. Он зевнул.</t>
+          <t>За последние шесть месяцев как часто увлечённо рассказывая о своей теме, вы замечаете лишь позже, что собеседник уже пытался сменить тему? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Замечаю зевок задним числом — увлёкся(лась) и не следил(а) за реакцией
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ASD 1]</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ASD 2]</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ASD 3]</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>Сразу сворачиваюсь: вижу, что неинтересно
-[]</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Обижаюсь: мог бы и послушать
-[NAR 1, PAG 1]</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Упрощаю объяснение
-[HUM 1]</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1493,7 +1522,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Систематизация и спектр</t>
+          <t>Переключение порядка</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1501,42 +1530,46 @@
           <t>ASD</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D18" s="4" t="inlineStr"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Коллега пишет в чат: «Глянешь мой отчёт, когда будет минутка?»</t>
+          <t>За последние шесть месяцев как часто вам трудно перейти к изменённому порядку обычных дел, даже когда причины изменения понятны? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Отвечаю «гляну» и ставлю напоминание на конкретное время: «когда будет минутка» мне ничего не говорит
-[ASD 3, OBC 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Посмотрю, когда освобожусь
-[]</t>
+          <t>Редко
+[ASD 1]</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Бросаю всё и смотрю: вдруг срочно
-[DEP 1, AVD 1]</t>
+          <t>Часто
+[ASD 2]</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Уточняю, к какому сроку нужно
-[OBC 1]</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[ASD 3]</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1544,7 +1577,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Право на отдых</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1555,35 +1588,43 @@
       <c r="D19" s="4" t="inlineStr"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Друзья зовут в поездку, а у вас скопилась работа, которую никто срочно не требует.</t>
+          <t>За последние шесть месяцев как часто вы отказываетесь от доступного и необходимого отдыха именно из-за мысли, что ещё не заслужили его? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Остаюсь работать: отдых надо заслужить
-[MAS 3, OBC 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Еду: работа подождёт
-[HIS 1]</t>
+          <t>Редко
+[MAS 1]</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Беру ноутбук с собой
-[OBC 2]</t>
+          <t>Часто
+[MAS 2]</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Еду, но всю поездку себя грызу
-[MAS 2, DPR 1]</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[MAS 3]</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1591,7 +1632,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Забота о здоровье</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1599,42 +1640,46 @@
           <t>MAS</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D20" s="4" t="inlineStr"/>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Врач советует несколько дней полежать дома.</t>
+          <t>За последние шесть месяцев как часто имея возможность восстановиться без потери необходимого дохода, вы всё равно лишаете себя отдыха, потому что заботиться о себе кажется незаслуженным? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, но «лежу» с ноутбуком и отвечаю на всё — так ведь все делают
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[MAS 1]</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[MAS 2]</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [MAS 3]</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>Честно отлёживаюсь
-[]</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>Выхожу на работу: без меня не справятся
-[NAR 1, MAS 1]</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>Пользуюсь случаем досмотреть сериалы
-[HIS 1]</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1642,7 +1687,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Право на удобство</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1653,35 +1698,43 @@
       <c r="D21" s="4" t="inlineStr"/>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>В гостях вам досталось самое неудобное место — табуретка у двери.</t>
+          <t>За последние шесть месяцев как часто вы терпите устранимое бытовое неудобство именно потому, что считаете собственный комфорт не заслуживающим внимания? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Так и сижу весь вечер: мне нормально, не хочу никого двигать
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[MAS 1]</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[MAS 2]</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [MAS 3]</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Прошу подвинуться
-[DIR 1]</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Обижаюсь, что обо мне не подумали
-[PAG 1, NAR 1]</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Весь вечер помогаю хозяевам
-[HUM 1, DEP 1]</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1689,7 +1742,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Принятие подарка</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1700,35 +1753,43 @@
       <c r="D22" s="4" t="inlineStr"/>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Вам сделали дорогой подарок — лично для вас.</t>
+          <t>За последние шесть месяцев как часто получая желанный подарок без условий, вы не можете принять радость из-за мысли, что не заслуживаете такого отношения? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Неловко до боли: я такого не стою
-[MAS 3, DEP 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Радуюсь от души
-[HIS 1]</t>
+          <t>Редко
+[MAS 1]</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Прикидываю, чем отдарить равноценно
-[OBC 1, KAN 1]</t>
+          <t>Часто
+[MAS 2]</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Подозреваю, чего от меня теперь хотят
-[PAR 2]</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[MAS 3]</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1736,7 +1797,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Признание вклада</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1744,42 +1805,46 @@
           <t>MAS</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D23" s="4" t="inlineStr"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Общий проект сдан, начальство хвалит команду. Больше всех тянули вы.</t>
+          <t>За последние шесть месяцев как часто когда ваш реальный вклад признают справедливо, вы отвергаете признание именно потому, что считаете себя его недостойными? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Молчу и отдаю заслуги другим — мне так спокойнее
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[MAS 1]</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[MAS 2]</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [MAS 3]</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Говорю, какую часть сделал(а) я
-[NAR 1, DIR 1]</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Радуюсь за всех вместе
-[HUM 1, FAI 1]</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Про себя злюсь, что меня не заметили
-[PAG 2]</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1787,7 +1852,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Границы помощи</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1798,35 +1863,43 @@
       <c r="D24" s="4" t="inlineStr"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Вы очень устали, а друг просит завтра в семь утра помочь с переездом.</t>
+          <t>За последние шесть месяцев как часто вы берёте на себя посильную для другого человека просьбу в ущерб собственному восстановлению, потому что свои потребности кажутся менее важными? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь, хотя еле стою: отказать — хуже, чем надорваться
-[MAS 3, DEP 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Отказываю: мне нужен отдых
-[]</t>
+          <t>Редко
+[MAS 1]</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Предлагаю помочь позже или по-другому
-[KAN 1]</t>
+          <t>Часто
+[MAS 2]</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Соглашаюсь и потом тихо злюсь
-[PAG 2]</t>
-        </is>
-      </c>
-      <c r="J24" s="4" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[MAS 3]</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1834,7 +1907,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Мазохизм (бета)</t>
+          <t>Доступное удобство</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1842,42 +1915,46 @@
           <t>MAS</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D25" s="4" t="inlineStr"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Вы выбираете рабочее кресло на годы вперёд.</t>
+          <t>За последние шесть месяцев как часто имея деньги на нужную вам удобную вещь без ущерба обязательным расходам, вы отказываетесь от неё именно потому, что не считаете себя достойными такого удобства? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Беру самое простое — мне хватит, лучше потрачу на близких
-[MAS 3, HUM 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Беру лучшее, что могу себе позволить: спина одна
-[]</t>
+          <t>Редко
+[MAS 1]</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Долго сравниваю характеристики
-[OBC 2]</t>
+          <t>Часто
+[MAS 2]</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Беру то, что посоветовали
-[DEP 1]</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[MAS 3]</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1885,7 +1962,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Определение чувства</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1896,35 +1973,43 @@
       <c r="D26" s="4" t="inlineStr"/>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Друг спрашивает, почему вы вчера так резко ушли с вечеринки.</t>
+          <t>За последние шесть месяцев как часто замечая эмоционально важную для вас реакцию, вы не можете понять, какое именно чувство испытываете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Пытаюсь объяснить — и понимаю, что сам(а) не знаю: просто стало «как-то не так»
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ALX 1]</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ALX 2]</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ALX 3]</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>Честно говорю: меня задела одна фраза
-[DIR 1]</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Придумываю вежливую причину
-[AVD 1, MAC 1]</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>Говорю, что устал(а), и не углубляюсь
-[ALX 1, SZD 1]</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1932,7 +2017,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Описание чувства</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1940,42 +2025,46 @@
           <t>ALX</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D27" s="4" t="inlineStr"/>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>После тяжёлого разговора с начальником коллега спрашивает: «Ты как?»</t>
+          <t>За последние шесть месяцев как часто желая рассказать близкому человеку о своём переживании, вы не находите слов для самого чувства, хотя события описать можете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Пересказываю по фактам: он сказал это, я ответил(а) то — разбирать разговор легче, чем чувства
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ALX 1]</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ALX 2]</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ALX 3]</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Говорю, что обидно и тревожно
-[]</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>«Нормально» — и меняю тему
-[ALX 2, AVD 1]</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>Злюсь вслух на начальника
-[PAG 1, ANT 1]</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1983,7 +2072,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Различение переживаний</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1994,35 +2083,43 @@
       <c r="D28" s="4" t="inlineStr"/>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>У вас без видимой причины колотится сердце и сжимается желудок.</t>
+          <t>За последние шесть месяцев как часто после напряжённого события вам трудно различить, что вы чувствуете: например, злость, страх или огорчение? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Думаю, что что-то с телом, — о чувствах вспоминаю в последнюю очередь
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ALX 1]</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ALX 2]</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ALX 3]</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>Понимаю: волнуюсь из-за завтрашнего
-[]</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>Иду проверяться к врачу
-[OBC 1, PAR 1]</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>Не обращаю внимания — пройдёт
-[MAS 1, ALX 1]</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2030,7 +2127,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Слова о тёплых чувствах</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2041,35 +2138,43 @@
       <c r="D29" s="4" t="inlineStr"/>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Нужно написать тёплое поздравление близкому человеку.</t>
+          <t>За последние шесть месяцев как часто испытывая тёплое чувство к близкому человеку и желая его выразить, вы затрудняетесь назвать это чувство своими словами? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Сижу над пустым листом: нужных слов о чувствах просто нет
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ALX 1]</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ALX 2]</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ALX 3]</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>Пишу легко — слова приходят сами
-[HIS 1]</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>Беру готовое поздравление из интернета
-[SZD 1, ALX 1]</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>Пишу коротко — и этого достаточно
-[DIR 1, SZD 1]</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr"/>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2077,7 +2182,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Замечание изменения состояния</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2085,42 +2190,46 @@
           <t>ALX</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
+      <c r="D30" s="4" t="inlineStr"/>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Близкий человек говорит: «Ты сегодня какой-то не такой».</t>
+          <t>За последние шесть месяцев как часто вы замечаете, что ваше эмоциональное состояние изменилось, но даже после размышления не можете понять, что именно чувствуете? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>«Да нет, всё как обычно» — и правда не замечаю в себе ничего особенного
+          <t>Никогда или почти никогда
+[]</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Редко
+[ALX 1]</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Часто
+[ALX 2]</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>Почти каждый раз
 [ALX 3]</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>Задумываюсь и понимаю, что с утра расстроен(а)
-[]</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>Раздражаюсь, что лезут в душу
-[AVD 1, PAG 1]</t>
-        </is>
-      </c>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>Спрашиваю, что именно заметили
-[DEP 1]</t>
-        </is>
-      </c>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2128,7 +2237,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Алекситимия</t>
+          <t>Внимание к переживанию</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -2139,41 +2248,49 @@
       <c r="D31" s="4" t="inlineStr"/>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Вы разбираете старые семейные фотографии.</t>
+          <t>За последние шесть месяцев как часто обдумывая значимое событие, вы возвращаетесь только к внешним фактам, потому что собственные переживания трудно удержать в поле внимания? Если таких ситуаций не было или ответить трудно, пропустите вопрос.</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Узнаю людей и места, но внутри почти ничего не шевелится
-[ALX 3, SZD 1]</t>
+          <t>Никогда или почти никогда
+[]</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Накатывает ностальгия, иногда до слёз
-[HIS 1]</t>
+          <t>Редко
+[ALX 1]</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Раскладываю их по годам и подписываю
-[OBC 2, ASD 1]</t>
+          <t>Часто
+[ALX 2]</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Становится грустно, и я их убираю
-[AVD 1, DPR 1]</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr"/>
+          <t>Почти каждый раз
+[ALX 3]</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Для пилота</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>Внутреннее ревью v2; интервью и валидация впереди</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K31"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править или Удалить" type="list">
-      <formula1>"ОК,Править,Удалить"</formula1>
+    <dataValidation sqref="J2:J31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Выберите: ОК, Править, Удалить или Для пилота" type="list">
+      <formula1>"ОК,Править,Удалить,Для пилота"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
